--- a/data/normalo2024.xlsx
+++ b/data/normalo2024.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabelhaas/Documents/Coding/aytogermany/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BC33FD-97A0-BE49-ACB5-CFEF0C624689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0339E33F-3DBB-3448-9BF5-5EBE2978AA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10620" yWindow="1060" windowWidth="26540" windowHeight="16160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="22140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Candidates" sheetId="1" r:id="rId1"/>
@@ -18,12 +13,12 @@
     <sheet name="Matchboxes" sheetId="3" r:id="rId3"/>
     <sheet name="Solution" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="33">
   <si>
     <t>left</t>
   </si>
@@ -106,14 +101,29 @@
     <t>episode</t>
   </si>
   <si>
+    <t>Mann</t>
+  </si>
+  <si>
+    <t>Frau</t>
+  </si>
+  <si>
     <t>result</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>before_night</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,10 +134,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -140,13 +153,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5C6C7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,13 +178,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -260,6 +271,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -294,6 +306,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -328,20 +341,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -463,7 +472,46 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -474,6 +522,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -582,6 +631,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -591,6 +641,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="11" width="10.6640625" customWidth="1"/>
+    <col min="12" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -980,32 +1031,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="24" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1015,11 +1071,14 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1029,11 +1088,14 @@
       <c r="C3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1043,11 +1105,14 @@
       <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1057,11 +1122,14 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1071,11 +1139,14 @@
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1085,11 +1156,14 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1099,11 +1173,14 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1113,11 +1190,14 @@
       <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" t="b">
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1127,11 +1207,14 @@
       <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>6</v>
       </c>
@@ -1141,11 +1224,14 @@
       <c r="C11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>7</v>
       </c>
@@ -1155,11 +1241,14 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>8</v>
       </c>
@@ -1169,12 +1258,16 @@
       <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
@@ -1182,6 +1275,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="24" width="13.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1288,6 +1384,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>